--- a/artfynd/A 29336-2026 artfynd.xlsx
+++ b/artfynd/A 29336-2026 artfynd.xlsx
@@ -3576,7 +3576,7 @@
         <v>454466</v>
       </c>
       <c r="R28" t="n">
-        <v>6785692</v>
+        <v>6785691</v>
       </c>
       <c r="S28" t="n">
         <v>7</v>
@@ -9539,7 +9539,7 @@
         <v>454466</v>
       </c>
       <c r="R81" t="n">
-        <v>6785692</v>
+        <v>6785691</v>
       </c>
       <c r="S81" t="n">
         <v>9</v>
@@ -14470,7 +14470,7 @@
         <v>454466</v>
       </c>
       <c r="R126" t="n">
-        <v>6785692</v>
+        <v>6785691</v>
       </c>
       <c r="S126" t="n">
         <v>7</v>

--- a/artfynd/A 29336-2026 artfynd.xlsx
+++ b/artfynd/A 29336-2026 artfynd.xlsx
@@ -3576,7 +3576,7 @@
         <v>454466</v>
       </c>
       <c r="R28" t="n">
-        <v>6785691</v>
+        <v>6785692</v>
       </c>
       <c r="S28" t="n">
         <v>7</v>
@@ -9539,7 +9539,7 @@
         <v>454466</v>
       </c>
       <c r="R81" t="n">
-        <v>6785691</v>
+        <v>6785692</v>
       </c>
       <c r="S81" t="n">
         <v>9</v>
@@ -14470,7 +14470,7 @@
         <v>454466</v>
       </c>
       <c r="R126" t="n">
-        <v>6785691</v>
+        <v>6785692</v>
       </c>
       <c r="S126" t="n">
         <v>7</v>

--- a/artfynd/A 29336-2026 artfynd.xlsx
+++ b/artfynd/A 29336-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY153"/>
+  <dimension ref="A1:AY162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9434,27 +9434,27 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135113657</v>
+        <v>135282299</v>
       </c>
       <c r="B81" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -9463,19 +9463,24 @@
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Björnkällan, Dlr</t>
+          <t>Skinnarbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>454244</v>
+        <v>454803</v>
       </c>
       <c r="R81" t="n">
-        <v>6785539</v>
+        <v>6785876</v>
       </c>
       <c r="S81" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9499,34 +9504,29 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>16:49</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Färsk bohåla, 3 m upp längs stammen på en levande gran.</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG81" t="b">
         <v>0</v>
@@ -9534,19 +9534,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Jenni Arvidsson</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135113674</v>
+        <v>135113657</v>
       </c>
       <c r="B82" t="n">
         <v>57975</v>
@@ -9575,31 +9575,19 @@
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Björnkällan, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>454395</v>
+        <v>454244</v>
       </c>
       <c r="R82" t="n">
-        <v>6785617</v>
+        <v>6785539</v>
       </c>
       <c r="S82" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9628,7 +9616,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9638,14 +9626,19 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Färsk bohåla, 3 m upp längs stammen på en levande gran.</t>
         </is>
       </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG82" t="b">
         <v>0</v>
@@ -9665,53 +9658,60 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135261577</v>
+        <v>135113674</v>
       </c>
       <c r="B83" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Björnkällan, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>454959</v>
+        <v>454395</v>
       </c>
       <c r="R83" t="n">
-        <v>6785933</v>
+        <v>6785617</v>
       </c>
       <c r="S83" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9735,22 +9735,22 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9770,17 +9770,17 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Eva Löfqvist, Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135115272</v>
+        <v>135261577</v>
       </c>
       <c r="B84" t="n">
-        <v>5181</v>
+        <v>57162</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9788,27 +9788,27 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9817,13 +9817,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>454223</v>
+        <v>454959</v>
       </c>
       <c r="R84" t="n">
-        <v>6785573</v>
+        <v>6785933</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9847,22 +9847,22 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>21:23</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>21:23</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9877,65 +9877,62 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135113626</v>
+        <v>135115272</v>
       </c>
       <c r="B85" t="n">
-        <v>58136</v>
+        <v>5181</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Björnkällan, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>454119</v>
+        <v>454223</v>
       </c>
       <c r="R85" t="n">
-        <v>6785539</v>
+        <v>6785573</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9967,7 +9964,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>21:23</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9977,7 +9974,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>21:23</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9992,44 +9989,44 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Jenni Arvidsson</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135113610</v>
+        <v>135113626</v>
       </c>
       <c r="B86" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10047,13 +10044,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>454108</v>
+        <v>454119</v>
       </c>
       <c r="R86" t="n">
-        <v>6785525</v>
+        <v>6785539</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10082,7 +10079,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10092,7 +10089,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10119,10 +10116,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>134934442</v>
+        <v>135113610</v>
       </c>
       <c r="B87" t="n">
-        <v>8460</v>
+        <v>58131</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10130,42 +10127,45 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>103023</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Björnkällan, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>454015</v>
+        <v>454108</v>
       </c>
       <c r="R87" t="n">
-        <v>6785466</v>
+        <v>6785525</v>
       </c>
       <c r="S87" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10189,22 +10189,22 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10224,14 +10224,14 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Eva Löfqvist, Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>134934450</v>
+        <v>134934442</v>
       </c>
       <c r="B88" t="n">
         <v>8460</v>
@@ -10262,7 +10262,7 @@
       <c r="I88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -10271,13 +10271,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>454141</v>
+        <v>454015</v>
       </c>
       <c r="R88" t="n">
-        <v>6785499</v>
+        <v>6785466</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10306,7 +10306,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10343,7 +10343,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>135115216</v>
+        <v>134934450</v>
       </c>
       <c r="B89" t="n">
         <v>8460</v>
@@ -10383,13 +10383,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>454082</v>
+        <v>454141</v>
       </c>
       <c r="R89" t="n">
-        <v>6785517</v>
+        <v>6785499</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10413,22 +10413,22 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10443,19 +10443,19 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>135261608</v>
+        <v>135115216</v>
       </c>
       <c r="B90" t="n">
         <v>8460</v>
@@ -10495,13 +10495,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>455033</v>
+        <v>454082</v>
       </c>
       <c r="R90" t="n">
-        <v>6785934</v>
+        <v>6785517</v>
       </c>
       <c r="S90" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10525,22 +10525,22 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10555,50 +10555,50 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>134934491</v>
+        <v>135261608</v>
       </c>
       <c r="B91" t="n">
-        <v>56539</v>
+        <v>8460</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>206004</v>
+        <v>106545</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -10607,10 +10607,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>454309</v>
+        <v>455033</v>
       </c>
       <c r="R91" t="n">
-        <v>6785656</v>
+        <v>6785934</v>
       </c>
       <c r="S91" t="n">
         <v>9</v>
@@ -10637,22 +10637,22 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10679,10 +10679,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>134934508</v>
+        <v>135282292</v>
       </c>
       <c r="B92" t="n">
-        <v>99112</v>
+        <v>8460</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10690,37 +10690,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>219790</v>
+        <v>106545</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Björnkällan, Dlr</t>
+          <t>Skinnarbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>454465</v>
+        <v>455037</v>
       </c>
       <c r="R92" t="n">
-        <v>6785647</v>
+        <v>6785955</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10744,22 +10744,22 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10770,26 +10770,36 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
+      </c>
+      <c r="AM92" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact</t>
+        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135066350</v>
+        <v>135282294</v>
       </c>
       <c r="B93" t="n">
-        <v>99112</v>
+        <v>8460</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10797,46 +10807,42 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>219790</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Björnkällan, Dlr</t>
+          <t>Skinnarbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>454251</v>
+        <v>454972</v>
       </c>
       <c r="R93" t="n">
-        <v>6785573</v>
+        <v>6785937</v>
       </c>
       <c r="S93" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10860,22 +10866,22 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10886,26 +10892,36 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
+      </c>
+      <c r="AM93" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags</t>
+        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>135066358</v>
+        <v>135282347</v>
       </c>
       <c r="B94" t="n">
-        <v>99112</v>
+        <v>8460</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10913,21 +10929,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>219790</v>
+        <v>106545</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10937,13 +10953,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>454288</v>
+        <v>454655</v>
       </c>
       <c r="R94" t="n">
-        <v>6785654</v>
+        <v>6785798</v>
       </c>
       <c r="S94" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10967,22 +10983,22 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10993,64 +11009,79 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
+      </c>
+      <c r="AM94" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags</t>
+        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135113660</v>
+        <v>134934491</v>
       </c>
       <c r="B95" t="n">
-        <v>99112</v>
+        <v>56539</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>219790</v>
+        <v>206004</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Björnkällan, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>454253</v>
+        <v>454309</v>
       </c>
       <c r="R95" t="n">
-        <v>6785549</v>
+        <v>6785656</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11074,22 +11105,22 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11116,10 +11147,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>134934459</v>
+        <v>134934508</v>
       </c>
       <c r="B96" t="n">
-        <v>111153</v>
+        <v>99112</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11127,21 +11158,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220240</v>
+        <v>219790</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11151,13 +11182,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>454157</v>
+        <v>454465</v>
       </c>
       <c r="R96" t="n">
-        <v>6785517</v>
+        <v>6785647</v>
       </c>
       <c r="S96" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11186,7 +11217,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11196,7 +11227,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11223,48 +11254,57 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>134934471</v>
+        <v>135066350</v>
       </c>
       <c r="B97" t="n">
-        <v>99195</v>
+        <v>99112</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Björnkällan, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>454263</v>
+        <v>454251</v>
       </c>
       <c r="R97" t="n">
-        <v>6785572</v>
+        <v>6785573</v>
       </c>
       <c r="S97" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11293,7 +11333,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11303,7 +11343,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11318,66 +11358,57 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>134934494</v>
+        <v>135066358</v>
       </c>
       <c r="B98" t="n">
-        <v>99195</v>
+        <v>99112</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Björnkällan, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>454344</v>
+        <v>454288</v>
       </c>
       <c r="R98" t="n">
-        <v>6785650</v>
+        <v>6785654</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11409,7 +11440,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11419,7 +11450,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11434,66 +11465,57 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>134934505</v>
+        <v>135113660</v>
       </c>
       <c r="B99" t="n">
-        <v>99195</v>
+        <v>99112</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Björnkällan, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>454452</v>
+        <v>454253</v>
       </c>
       <c r="R99" t="n">
-        <v>6785662</v>
+        <v>6785549</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11520,22 +11542,22 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11562,57 +11584,57 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>134934507</v>
+        <v>135282298</v>
       </c>
       <c r="B100" t="n">
-        <v>99195</v>
+        <v>99112</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Björnkällan, Dlr</t>
+          <t>Skinnarbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>454460</v>
+        <v>454873</v>
       </c>
       <c r="R100" t="n">
-        <v>6785644</v>
+        <v>6785914</v>
       </c>
       <c r="S100" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11636,22 +11658,22 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11666,69 +11688,60 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>134934510</v>
+        <v>134934459</v>
       </c>
       <c r="B101" t="n">
-        <v>99195</v>
+        <v>111153</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>220240</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Björnkällan, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>454459</v>
+        <v>454157</v>
       </c>
       <c r="R101" t="n">
-        <v>6785696</v>
+        <v>6785517</v>
       </c>
       <c r="S101" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11757,7 +11770,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11767,7 +11780,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11794,7 +11807,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>134934513</v>
+        <v>134934471</v>
       </c>
       <c r="B102" t="n">
         <v>99195</v>
@@ -11822,29 +11835,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Björnkällan, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>454466</v>
+        <v>454263</v>
       </c>
       <c r="R102" t="n">
-        <v>6785692</v>
+        <v>6785572</v>
       </c>
       <c r="S102" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11873,7 +11877,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11883,7 +11887,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11910,7 +11914,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>134934519</v>
+        <v>134934494</v>
       </c>
       <c r="B103" t="n">
         <v>99195</v>
@@ -11940,12 +11944,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -11954,13 +11958,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>454508</v>
+        <v>454344</v>
       </c>
       <c r="R103" t="n">
-        <v>6785716</v>
+        <v>6785650</v>
       </c>
       <c r="S103" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11989,7 +11993,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>20:56</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11999,7 +12003,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>20:56</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12026,7 +12030,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>134934521</v>
+        <v>134934505</v>
       </c>
       <c r="B104" t="n">
         <v>99195</v>
@@ -12056,12 +12060,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -12070,10 +12074,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>454531</v>
+        <v>454452</v>
       </c>
       <c r="R104" t="n">
-        <v>6785706</v>
+        <v>6785662</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -12105,7 +12109,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>21:11</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12115,7 +12119,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>21:11</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12142,7 +12146,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>135066302</v>
+        <v>134934507</v>
       </c>
       <c r="B105" t="n">
         <v>99195</v>
@@ -12172,7 +12176,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -12186,13 +12190,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>454474</v>
+        <v>454460</v>
       </c>
       <c r="R105" t="n">
-        <v>6785691</v>
+        <v>6785644</v>
       </c>
       <c r="S105" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12221,7 +12225,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12231,7 +12235,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12246,19 +12250,19 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>135066303</v>
+        <v>134934510</v>
       </c>
       <c r="B106" t="n">
         <v>99195</v>
@@ -12288,7 +12292,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -12302,13 +12306,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>454474</v>
+        <v>454459</v>
       </c>
       <c r="R106" t="n">
         <v>6785696</v>
       </c>
       <c r="S106" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12337,7 +12341,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12347,7 +12351,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12362,19 +12366,19 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>135066361</v>
+        <v>134934513</v>
       </c>
       <c r="B107" t="n">
         <v>99195</v>
@@ -12404,12 +12408,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -12418,13 +12422,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>454356</v>
+        <v>454466</v>
       </c>
       <c r="R107" t="n">
-        <v>6785641</v>
+        <v>6785692</v>
       </c>
       <c r="S107" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12453,7 +12457,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12463,7 +12467,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12478,19 +12482,19 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>135066364</v>
+        <v>134934519</v>
       </c>
       <c r="B108" t="n">
         <v>99195</v>
@@ -12534,13 +12538,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>454382</v>
+        <v>454508</v>
       </c>
       <c r="R108" t="n">
-        <v>6785657</v>
+        <v>6785716</v>
       </c>
       <c r="S108" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12569,7 +12573,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>19:27</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12579,7 +12583,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>19:27</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12594,19 +12598,19 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>135113598</v>
+        <v>134934521</v>
       </c>
       <c r="B109" t="n">
         <v>99195</v>
@@ -12636,12 +12640,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -12650,13 +12654,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>454051</v>
+        <v>454531</v>
       </c>
       <c r="R109" t="n">
-        <v>6785463</v>
+        <v>6785706</v>
       </c>
       <c r="S109" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12680,22 +12684,22 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12722,7 +12726,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>135113606</v>
+        <v>135066302</v>
       </c>
       <c r="B110" t="n">
         <v>99195</v>
@@ -12752,7 +12756,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -12760,22 +12764,19 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Björnkällan, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>454109</v>
+        <v>454474</v>
       </c>
       <c r="R110" t="n">
-        <v>6785533</v>
+        <v>6785691</v>
       </c>
       <c r="S110" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12799,22 +12800,22 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12823,26 +12824,25 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Jenni Arvidsson</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>135113658</v>
+        <v>135066303</v>
       </c>
       <c r="B111" t="n">
         <v>99195</v>
@@ -12872,7 +12872,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -12880,22 +12880,19 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Björnkällan, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>454244</v>
+        <v>454474</v>
       </c>
       <c r="R111" t="n">
-        <v>6785539</v>
+        <v>6785696</v>
       </c>
       <c r="S111" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12919,22 +12916,22 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12943,26 +12940,25 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Jenni Arvidsson</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>135115221</v>
+        <v>135066361</v>
       </c>
       <c r="B112" t="n">
         <v>99195</v>
@@ -12992,7 +12988,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -13006,10 +13002,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>454115</v>
+        <v>454356</v>
       </c>
       <c r="R112" t="n">
-        <v>6785571</v>
+        <v>6785641</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -13036,22 +13032,22 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13078,48 +13074,57 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>134934523</v>
+        <v>135066364</v>
       </c>
       <c r="B113" t="n">
-        <v>109924</v>
+        <v>99195</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>221184</v>
+        <v>220787</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Björnkällan, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>454546</v>
+        <v>454382</v>
       </c>
       <c r="R113" t="n">
-        <v>6785757</v>
+        <v>6785657</v>
       </c>
       <c r="S113" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -13148,7 +13153,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>21:18</t>
+          <t>19:27</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13158,7 +13163,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>21:18</t>
+          <t>19:27</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13173,60 +13178,69 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>135066357</v>
+        <v>135113598</v>
       </c>
       <c r="B114" t="n">
-        <v>109924</v>
+        <v>99195</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>221184</v>
+        <v>220787</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Björnkällan, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>454299</v>
+        <v>454051</v>
       </c>
       <c r="R114" t="n">
-        <v>6785657</v>
+        <v>6785463</v>
       </c>
       <c r="S114" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13250,22 +13264,22 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13280,60 +13294,72 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>135113591</v>
+        <v>135113606</v>
       </c>
       <c r="B115" t="n">
-        <v>98066</v>
+        <v>99195</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Björnkällan, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>453988</v>
+        <v>454109</v>
       </c>
       <c r="R115" t="n">
-        <v>6785416</v>
+        <v>6785533</v>
       </c>
       <c r="S115" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13362,7 +13388,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13372,7 +13398,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13381,6 +13407,7 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -13392,55 +13419,67 @@
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Eva Löfqvist, Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>135115213</v>
+        <v>135113658</v>
       </c>
       <c r="B116" t="n">
-        <v>98066</v>
+        <v>99195</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Björnkällan, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>454066</v>
+        <v>454244</v>
       </c>
       <c r="R116" t="n">
-        <v>6785506</v>
+        <v>6785539</v>
       </c>
       <c r="S116" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13469,7 +13508,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13479,7 +13518,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13488,63 +13527,73 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist, Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>134934449</v>
+        <v>135115221</v>
       </c>
       <c r="B117" t="n">
-        <v>98060</v>
+        <v>99195</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Björnkällan, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>454135</v>
+        <v>454115</v>
       </c>
       <c r="R117" t="n">
-        <v>6785490</v>
+        <v>6785571</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -13571,22 +13620,22 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13601,57 +13650,66 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>135066359</v>
+        <v>135282297</v>
       </c>
       <c r="B118" t="n">
-        <v>98060</v>
+        <v>99195</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Björnkällan, Dlr</t>
+          <t>Skinnarbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>454288</v>
+        <v>454941</v>
       </c>
       <c r="R118" t="n">
-        <v>6785654</v>
+        <v>6785935</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13678,22 +13736,22 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13708,22 +13766,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>135066363</v>
+        <v>134934523</v>
       </c>
       <c r="B119" t="n">
-        <v>98060</v>
+        <v>109924</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13731,21 +13789,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>221945</v>
+        <v>221184</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13755,13 +13813,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>454380</v>
+        <v>454546</v>
       </c>
       <c r="R119" t="n">
-        <v>6785659</v>
+        <v>6785757</v>
       </c>
       <c r="S119" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13790,7 +13848,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>19:27</t>
+          <t>21:18</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13800,7 +13858,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>19:27</t>
+          <t>21:18</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13815,22 +13873,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>135113605</v>
+        <v>135066357</v>
       </c>
       <c r="B120" t="n">
-        <v>98060</v>
+        <v>109924</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13838,21 +13896,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>221945</v>
+        <v>221184</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13862,13 +13920,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>454107</v>
+        <v>454299</v>
       </c>
       <c r="R120" t="n">
-        <v>6785533</v>
+        <v>6785657</v>
       </c>
       <c r="S120" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13892,22 +13950,22 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13922,22 +13980,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>135113701</v>
+        <v>135113591</v>
       </c>
       <c r="B121" t="n">
-        <v>98060</v>
+        <v>98066</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13945,16 +14003,16 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -13969,10 +14027,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>454301</v>
+        <v>453988</v>
       </c>
       <c r="R121" t="n">
-        <v>6785611</v>
+        <v>6785416</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -14004,7 +14062,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>21:16</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14014,7 +14072,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>21:16</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14041,10 +14099,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>135115204</v>
+        <v>135115213</v>
       </c>
       <c r="B122" t="n">
-        <v>98060</v>
+        <v>98066</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14052,16 +14110,16 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -14076,10 +14134,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>454006</v>
+        <v>454066</v>
       </c>
       <c r="R122" t="n">
-        <v>6785442</v>
+        <v>6785506</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -14111,7 +14169,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14121,7 +14179,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14148,7 +14206,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>135115248</v>
+        <v>134934449</v>
       </c>
       <c r="B123" t="n">
         <v>98060</v>
@@ -14183,10 +14241,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>454288</v>
+        <v>454135</v>
       </c>
       <c r="R123" t="n">
-        <v>6785614</v>
+        <v>6785490</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -14213,22 +14271,22 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14243,19 +14301,19 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>135261580</v>
+        <v>135066359</v>
       </c>
       <c r="B124" t="n">
         <v>98060</v>
@@ -14290,13 +14348,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>454955</v>
+        <v>454288</v>
       </c>
       <c r="R124" t="n">
-        <v>6785927</v>
+        <v>6785654</v>
       </c>
       <c r="S124" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14320,22 +14378,22 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14350,19 +14408,19 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>135261592</v>
+        <v>135066363</v>
       </c>
       <c r="B125" t="n">
         <v>98060</v>
@@ -14397,13 +14455,13 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>454861</v>
+        <v>454380</v>
       </c>
       <c r="R125" t="n">
-        <v>6785899</v>
+        <v>6785659</v>
       </c>
       <c r="S125" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14427,22 +14485,22 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:27</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:27</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14457,19 +14515,19 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>135261594</v>
+        <v>135113605</v>
       </c>
       <c r="B126" t="n">
         <v>98060</v>
@@ -14504,10 +14562,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>454784</v>
+        <v>454107</v>
       </c>
       <c r="R126" t="n">
-        <v>6785860</v>
+        <v>6785533</v>
       </c>
       <c r="S126" t="n">
         <v>6</v>
@@ -14534,22 +14592,22 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14576,10 +14634,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>134934453</v>
+        <v>135113701</v>
       </c>
       <c r="B127" t="n">
-        <v>99217</v>
+        <v>98060</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14587,21 +14645,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14611,10 +14669,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>454145</v>
+        <v>454301</v>
       </c>
       <c r="R127" t="n">
-        <v>6785517</v>
+        <v>6785611</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -14641,22 +14699,22 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>21:16</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>21:16</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14683,10 +14741,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>134934465</v>
+        <v>135115204</v>
       </c>
       <c r="B128" t="n">
-        <v>99217</v>
+        <v>98060</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14694,21 +14752,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14718,10 +14776,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>454209</v>
+        <v>454006</v>
       </c>
       <c r="R128" t="n">
-        <v>6785612</v>
+        <v>6785442</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -14748,22 +14806,22 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14778,22 +14836,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>134934467</v>
+        <v>135115248</v>
       </c>
       <c r="B129" t="n">
-        <v>99217</v>
+        <v>98060</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14801,21 +14859,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14825,10 +14883,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>454239</v>
+        <v>454288</v>
       </c>
       <c r="R129" t="n">
-        <v>6785592</v>
+        <v>6785614</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -14855,22 +14913,22 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14885,22 +14943,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>134934468</v>
+        <v>135261580</v>
       </c>
       <c r="B130" t="n">
-        <v>99217</v>
+        <v>98060</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14908,21 +14966,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14932,10 +14990,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>454254</v>
+        <v>454955</v>
       </c>
       <c r="R130" t="n">
-        <v>6785598</v>
+        <v>6785927</v>
       </c>
       <c r="S130" t="n">
         <v>8</v>
@@ -14962,22 +15020,22 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15004,10 +15062,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>134934469</v>
+        <v>135261592</v>
       </c>
       <c r="B131" t="n">
-        <v>99217</v>
+        <v>98060</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15015,21 +15073,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -15039,13 +15097,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>454263</v>
+        <v>454861</v>
       </c>
       <c r="R131" t="n">
-        <v>6785579</v>
+        <v>6785899</v>
       </c>
       <c r="S131" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15069,22 +15127,22 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15111,10 +15169,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>134934473</v>
+        <v>135261594</v>
       </c>
       <c r="B132" t="n">
-        <v>99217</v>
+        <v>98060</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15122,21 +15180,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -15146,10 +15204,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>454256</v>
+        <v>454784</v>
       </c>
       <c r="R132" t="n">
-        <v>6785560</v>
+        <v>6785860</v>
       </c>
       <c r="S132" t="n">
         <v>6</v>
@@ -15176,22 +15234,22 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15218,10 +15276,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>134934490</v>
+        <v>135282290</v>
       </c>
       <c r="B133" t="n">
-        <v>99217</v>
+        <v>98060</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15229,37 +15287,46 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Björnkällan, Dlr</t>
+          <t>Skinnarbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>454302</v>
+        <v>455082</v>
       </c>
       <c r="R133" t="n">
-        <v>6785652</v>
+        <v>6786014</v>
       </c>
       <c r="S133" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -15283,22 +15350,22 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15313,22 +15380,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>134934498</v>
+        <v>135282295</v>
       </c>
       <c r="B134" t="n">
-        <v>99217</v>
+        <v>98060</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15336,37 +15403,37 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Björnkällan, Dlr</t>
+          <t>Skinnarbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>454389</v>
+        <v>454957</v>
       </c>
       <c r="R134" t="n">
-        <v>6785645</v>
+        <v>6785927</v>
       </c>
       <c r="S134" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -15390,22 +15457,22 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15420,19 +15487,19 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>134934515</v>
+        <v>134934453</v>
       </c>
       <c r="B135" t="n">
         <v>99217</v>
@@ -15467,13 +15534,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>454489</v>
+        <v>454145</v>
       </c>
       <c r="R135" t="n">
-        <v>6785704</v>
+        <v>6785517</v>
       </c>
       <c r="S135" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15502,7 +15569,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15512,7 +15579,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15539,7 +15606,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>134934517</v>
+        <v>134934465</v>
       </c>
       <c r="B136" t="n">
         <v>99217</v>
@@ -15574,13 +15641,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>454497</v>
+        <v>454209</v>
       </c>
       <c r="R136" t="n">
-        <v>6785714</v>
+        <v>6785612</v>
       </c>
       <c r="S136" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15609,7 +15676,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>20:48</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15619,7 +15686,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>20:48</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15646,7 +15713,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>134934522</v>
+        <v>134934467</v>
       </c>
       <c r="B137" t="n">
         <v>99217</v>
@@ -15681,13 +15748,13 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>454546</v>
+        <v>454239</v>
       </c>
       <c r="R137" t="n">
-        <v>6785757</v>
+        <v>6785592</v>
       </c>
       <c r="S137" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15716,7 +15783,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15726,7 +15793,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15753,7 +15820,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>134934524</v>
+        <v>134934468</v>
       </c>
       <c r="B138" t="n">
         <v>99217</v>
@@ -15788,13 +15855,13 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>454590</v>
+        <v>454254</v>
       </c>
       <c r="R138" t="n">
-        <v>6785754</v>
+        <v>6785598</v>
       </c>
       <c r="S138" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15823,7 +15890,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>21:26</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15833,7 +15900,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>21:26</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15860,7 +15927,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>135066304</v>
+        <v>134934469</v>
       </c>
       <c r="B139" t="n">
         <v>99217</v>
@@ -15895,13 +15962,13 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>454488</v>
+        <v>454263</v>
       </c>
       <c r="R139" t="n">
-        <v>6785702</v>
+        <v>6785579</v>
       </c>
       <c r="S139" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -15930,7 +15997,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15940,7 +16007,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15955,19 +16022,19 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>135066306</v>
+        <v>134934473</v>
       </c>
       <c r="B140" t="n">
         <v>99217</v>
@@ -16002,13 +16069,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>454506</v>
+        <v>454256</v>
       </c>
       <c r="R140" t="n">
-        <v>6785707</v>
+        <v>6785560</v>
       </c>
       <c r="S140" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16037,7 +16104,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -16047,7 +16114,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16062,19 +16129,19 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>135066348</v>
+        <v>134934490</v>
       </c>
       <c r="B141" t="n">
         <v>99217</v>
@@ -16102,29 +16169,20 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Björnkällan, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>454217</v>
+        <v>454302</v>
       </c>
       <c r="R141" t="n">
-        <v>6785616</v>
+        <v>6785652</v>
       </c>
       <c r="S141" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -16153,7 +16211,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -16163,7 +16221,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16178,19 +16236,19 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>135066349</v>
+        <v>134934498</v>
       </c>
       <c r="B142" t="n">
         <v>99217</v>
@@ -16218,29 +16276,20 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Björnkällan, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>454234</v>
+        <v>454389</v>
       </c>
       <c r="R142" t="n">
-        <v>6785600</v>
+        <v>6785645</v>
       </c>
       <c r="S142" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -16269,7 +16318,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -16279,7 +16328,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16294,19 +16343,19 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>135066351</v>
+        <v>134934515</v>
       </c>
       <c r="B143" t="n">
         <v>99217</v>
@@ -16341,13 +16390,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>454251</v>
+        <v>454489</v>
       </c>
       <c r="R143" t="n">
-        <v>6785563</v>
+        <v>6785704</v>
       </c>
       <c r="S143" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -16376,7 +16425,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -16386,7 +16435,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16401,19 +16450,19 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>135113594</v>
+        <v>134934517</v>
       </c>
       <c r="B144" t="n">
         <v>99217</v>
@@ -16448,13 +16497,13 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>454014</v>
+        <v>454497</v>
       </c>
       <c r="R144" t="n">
-        <v>6785459</v>
+        <v>6785714</v>
       </c>
       <c r="S144" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -16478,22 +16527,22 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>20:48</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>20:48</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16520,7 +16569,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>135113607</v>
+        <v>134934522</v>
       </c>
       <c r="B145" t="n">
         <v>99217</v>
@@ -16555,13 +16604,13 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>454109</v>
+        <v>454546</v>
       </c>
       <c r="R145" t="n">
-        <v>6785533</v>
+        <v>6785757</v>
       </c>
       <c r="S145" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -16585,22 +16634,22 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16627,7 +16676,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>135113613</v>
+        <v>134934524</v>
       </c>
       <c r="B146" t="n">
         <v>99217</v>
@@ -16662,13 +16711,13 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>454130</v>
+        <v>454590</v>
       </c>
       <c r="R146" t="n">
-        <v>6785556</v>
+        <v>6785754</v>
       </c>
       <c r="S146" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -16692,22 +16741,22 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>21:26</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>21:26</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16734,7 +16783,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>135113625</v>
+        <v>135066304</v>
       </c>
       <c r="B147" t="n">
         <v>99217</v>
@@ -16769,10 +16818,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>454119</v>
+        <v>454488</v>
       </c>
       <c r="R147" t="n">
-        <v>6785539</v>
+        <v>6785702</v>
       </c>
       <c r="S147" t="n">
         <v>5</v>
@@ -16799,22 +16848,22 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16829,19 +16878,19 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>135113703</v>
+        <v>135066306</v>
       </c>
       <c r="B148" t="n">
         <v>99217</v>
@@ -16876,10 +16925,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>454214</v>
+        <v>454506</v>
       </c>
       <c r="R148" t="n">
-        <v>6785559</v>
+        <v>6785707</v>
       </c>
       <c r="S148" t="n">
         <v>5</v>
@@ -16906,22 +16955,22 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>21:26</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>21:26</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16936,19 +16985,19 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>135113704</v>
+        <v>135066348</v>
       </c>
       <c r="B149" t="n">
         <v>99217</v>
@@ -16976,20 +17025,29 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr"/>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Björnkällan, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>454197</v>
+        <v>454217</v>
       </c>
       <c r="R149" t="n">
-        <v>6785529</v>
+        <v>6785616</v>
       </c>
       <c r="S149" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -17013,22 +17071,22 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>21:29</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>21:29</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17043,19 +17101,19 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>135261587</v>
+        <v>135066349</v>
       </c>
       <c r="B150" t="n">
         <v>99217</v>
@@ -17083,17 +17141,26 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr"/>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Björnkällan, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>454920</v>
+        <v>454234</v>
       </c>
       <c r="R150" t="n">
-        <v>6785935</v>
+        <v>6785600</v>
       </c>
       <c r="S150" t="n">
         <v>5</v>
@@ -17120,22 +17187,22 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17150,19 +17217,19 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>135261607</v>
+        <v>135066351</v>
       </c>
       <c r="B151" t="n">
         <v>99217</v>
@@ -17197,10 +17264,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>454540</v>
+        <v>454251</v>
       </c>
       <c r="R151" t="n">
-        <v>6785772</v>
+        <v>6785563</v>
       </c>
       <c r="S151" t="n">
         <v>5</v>
@@ -17227,22 +17294,22 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17257,22 +17324,22 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>134934512</v>
+        <v>135113594</v>
       </c>
       <c r="B152" t="n">
-        <v>103907</v>
+        <v>99217</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17280,21 +17347,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>223284</v>
+        <v>221952</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -17304,13 +17371,13 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>454466</v>
+        <v>454014</v>
       </c>
       <c r="R152" t="n">
-        <v>6785692</v>
+        <v>6785459</v>
       </c>
       <c r="S152" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -17334,27 +17401,22 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>20:28</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>55 cm i omkrets.</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17381,10 +17443,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>135261588</v>
+        <v>135113607</v>
       </c>
       <c r="B153" t="n">
-        <v>103907</v>
+        <v>99217</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17392,21 +17454,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>223284</v>
+        <v>221952</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -17416,13 +17478,13 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>454905</v>
+        <v>454109</v>
       </c>
       <c r="R153" t="n">
-        <v>6785917</v>
+        <v>6785533</v>
       </c>
       <c r="S153" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -17446,27 +17508,22 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>19:14</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>105 cm i omkrets.</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17490,6 +17547,988 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>135113613</v>
+      </c>
+      <c r="B154" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Björnkällan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>454130</v>
+      </c>
+      <c r="R154" t="n">
+        <v>6785556</v>
+      </c>
+      <c r="S154" t="n">
+        <v>5</v>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT154" t="inlineStr"/>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>135113625</v>
+      </c>
+      <c r="B155" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Björnkällan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>454119</v>
+      </c>
+      <c r="R155" t="n">
+        <v>6785539</v>
+      </c>
+      <c r="S155" t="n">
+        <v>5</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT155" t="inlineStr"/>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>135113703</v>
+      </c>
+      <c r="B156" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Björnkällan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>454214</v>
+      </c>
+      <c r="R156" t="n">
+        <v>6785559</v>
+      </c>
+      <c r="S156" t="n">
+        <v>5</v>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>21:26</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>21:26</t>
+        </is>
+      </c>
+      <c r="AD156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT156" t="inlineStr"/>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>135113704</v>
+      </c>
+      <c r="B157" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Björnkällan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>454197</v>
+      </c>
+      <c r="R157" t="n">
+        <v>6785529</v>
+      </c>
+      <c r="S157" t="n">
+        <v>7</v>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>21:29</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>21:29</t>
+        </is>
+      </c>
+      <c r="AD157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT157" t="inlineStr"/>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>135261587</v>
+      </c>
+      <c r="B158" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Björnkällan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>454920</v>
+      </c>
+      <c r="R158" t="n">
+        <v>6785935</v>
+      </c>
+      <c r="S158" t="n">
+        <v>5</v>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>19:08</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>19:08</t>
+        </is>
+      </c>
+      <c r="AD158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT158" t="inlineStr"/>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>135261607</v>
+      </c>
+      <c r="B159" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Björnkällan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>454540</v>
+      </c>
+      <c r="R159" t="n">
+        <v>6785772</v>
+      </c>
+      <c r="S159" t="n">
+        <v>5</v>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="AD159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT159" t="inlineStr"/>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>135282296</v>
+      </c>
+      <c r="B160" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Skinnarbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>454952</v>
+      </c>
+      <c r="R160" t="n">
+        <v>6785931</v>
+      </c>
+      <c r="S160" t="n">
+        <v>5</v>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="AD160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT160" t="inlineStr"/>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>134934512</v>
+      </c>
+      <c r="B161" t="n">
+        <v>103907</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>Björnkällan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q161" t="n">
+        <v>454466</v>
+      </c>
+      <c r="R161" t="n">
+        <v>6785692</v>
+      </c>
+      <c r="S161" t="n">
+        <v>7</v>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>20:28</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>20:28</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>55 cm i omkrets.</t>
+        </is>
+      </c>
+      <c r="AD161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT161" t="inlineStr"/>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>135261588</v>
+      </c>
+      <c r="B162" t="n">
+        <v>103907</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>Björnkällan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q162" t="n">
+        <v>454905</v>
+      </c>
+      <c r="R162" t="n">
+        <v>6785917</v>
+      </c>
+      <c r="S162" t="n">
+        <v>6</v>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>19:14</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>19:14</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>105 cm i omkrets.</t>
+        </is>
+      </c>
+      <c r="AD162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT162" t="inlineStr"/>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29336-2026 artfynd.xlsx
+++ b/artfynd/A 29336-2026 artfynd.xlsx
@@ -3810,7 +3810,7 @@
         <v>454466</v>
       </c>
       <c r="R30" t="n">
-        <v>6785692</v>
+        <v>6785691</v>
       </c>
       <c r="S30" t="n">
         <v>7</v>
@@ -12425,7 +12425,7 @@
         <v>454466</v>
       </c>
       <c r="R107" t="n">
-        <v>6785692</v>
+        <v>6785691</v>
       </c>
       <c r="S107" t="n">
         <v>9</v>
@@ -18346,7 +18346,7 @@
         <v>454466</v>
       </c>
       <c r="R161" t="n">
-        <v>6785692</v>
+        <v>6785691</v>
       </c>
       <c r="S161" t="n">
         <v>7</v>

--- a/artfynd/A 29336-2026 artfynd.xlsx
+++ b/artfynd/A 29336-2026 artfynd.xlsx
@@ -3810,7 +3810,7 @@
         <v>454466</v>
       </c>
       <c r="R30" t="n">
-        <v>6785691</v>
+        <v>6785692</v>
       </c>
       <c r="S30" t="n">
         <v>7</v>
@@ -12425,7 +12425,7 @@
         <v>454466</v>
       </c>
       <c r="R107" t="n">
-        <v>6785691</v>
+        <v>6785692</v>
       </c>
       <c r="S107" t="n">
         <v>9</v>
@@ -18346,7 +18346,7 @@
         <v>454466</v>
       </c>
       <c r="R161" t="n">
-        <v>6785691</v>
+        <v>6785692</v>
       </c>
       <c r="S161" t="n">
         <v>7</v>

--- a/artfynd/A 29336-2026 artfynd.xlsx
+++ b/artfynd/A 29336-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY162"/>
+  <dimension ref="A1:AZ162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934447</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934448</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934462</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135113596</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135115205</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1339,6 +1369,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135115212</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1446,6 +1481,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261522</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1553,6 +1593,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934475</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1664,6 +1709,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934472</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1771,6 +1821,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934474</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1878,6 +1933,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934486</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1985,6 +2045,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934470</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2116,6 +2181,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135113602</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2243,6 +2313,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135113611</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2370,6 +2445,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261584</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2477,6 +2557,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934458</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2584,6 +2669,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934460</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2691,6 +2781,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934461</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2798,6 +2893,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934463</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2905,6 +3005,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934464</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3012,6 +3117,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934466</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3119,6 +3229,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934485</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3226,6 +3341,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934495</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3341,6 +3461,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934496</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3448,6 +3573,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934497</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3555,6 +3685,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934500</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3662,6 +3797,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934504</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3769,6 +3909,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934509</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3876,6 +4021,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934511</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3993,6 +4143,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135066305</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4110,6 +4265,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135066344</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4227,6 +4387,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135066346</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4344,6 +4509,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135066365</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4461,6 +4631,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135066367</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4568,6 +4743,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135113592</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4675,6 +4855,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135113595</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4782,6 +4967,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135113597</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4889,6 +5079,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135113599</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4996,6 +5191,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135113604</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5103,6 +5303,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135113609</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5210,6 +5415,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135113612</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5317,6 +5527,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135113628</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5424,6 +5639,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135113630</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5531,6 +5751,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135113661</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5643,6 +5868,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135113702</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5760,6 +5990,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135115208</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5877,6 +6112,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135115210</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5994,6 +6234,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135115214</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6111,6 +6356,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135115218</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6228,6 +6478,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135115225</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6335,6 +6590,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261576</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6442,6 +6702,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261578</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6549,6 +6814,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261589</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6656,6 +6926,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261593</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6763,6 +7038,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261596</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6870,6 +7150,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261597</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6977,6 +7262,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261599</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7084,6 +7374,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261600</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7191,6 +7486,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261601</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7298,6 +7598,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261602</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7424,6 +7729,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934518</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7531,6 +7841,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261604</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7638,6 +7953,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135113601</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7745,6 +8065,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261520</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7857,6 +8182,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934455</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7969,6 +8299,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934516</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8081,6 +8416,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934520</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8196,6 +8536,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135066308</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8308,6 +8653,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135066353</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8420,6 +8770,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135113623</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8532,6 +8887,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135113675</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8647,6 +9007,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135115215</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8759,6 +9124,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135115247</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8871,6 +9241,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135115277</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8983,6 +9358,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261518</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9095,6 +9475,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261519</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9207,6 +9592,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261521</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9319,6 +9709,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261595</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9431,6 +9826,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261606</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9543,6 +9943,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135282299</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9655,6 +10060,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135113657</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9774,6 +10184,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135113674</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9886,6 +10301,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261577</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9998,6 +10418,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135115272</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10113,6 +10538,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135113626</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10228,6 +10658,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135113610</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10340,6 +10775,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934442</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10452,6 +10892,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934450</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10564,6 +11009,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135115216</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10676,6 +11126,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261608</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10793,6 +11248,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135282292</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10915,6 +11375,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135282294</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11032,6 +11497,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135282347</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11144,6 +11614,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934491</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11251,6 +11726,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934508</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11367,6 +11847,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135066350</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11474,6 +11959,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135066358</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11581,6 +12071,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135113660</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11697,6 +12192,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135282298</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11804,6 +12304,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934459</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11911,6 +12416,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934471</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12027,6 +12537,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934494</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12143,6 +12658,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934505</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12259,6 +12779,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934507</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12375,6 +12900,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934510</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12491,6 +13021,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934513</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12607,6 +13142,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934519</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12723,6 +13263,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934521</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12839,6 +13384,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135066302</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12955,6 +13505,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135066303</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13071,6 +13626,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135066361</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13187,6 +13747,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135066364</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13303,6 +13868,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135113598</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13423,6 +13993,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135113606</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13543,6 +14118,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135113658</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13659,6 +14239,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135115221</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13775,6 +14360,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135282297</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13882,6 +14472,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934523</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13989,6 +14584,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135066357</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14096,6 +14696,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135113591</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14203,6 +14808,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135115213</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14310,6 +14920,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934449</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14417,6 +15032,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135066359</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14524,6 +15144,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135066363</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14631,6 +15256,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135113605</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14738,6 +15368,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135113701</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14845,6 +15480,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135115204</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14952,6 +15592,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135115248</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15059,6 +15704,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261580</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15166,6 +15816,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261592</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15273,6 +15928,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261594</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15389,6 +16049,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135282290</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15496,6 +16161,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135282295</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15603,6 +16273,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934453</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15710,6 +16385,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934465</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15817,6 +16497,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934467</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15924,6 +16609,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934468</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -16031,6 +16721,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934469</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16138,6 +16833,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934473</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16245,6 +16945,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934490</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16352,6 +17057,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934498</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16459,6 +17169,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934515</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16566,6 +17281,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934517</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16673,6 +17393,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934522</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16780,6 +17505,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934524</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16887,6 +17617,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135066304</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16994,6 +17729,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135066306</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -17110,6 +17850,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135066348</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -17226,6 +17971,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135066349</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -17333,6 +18083,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135066351</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17440,6 +18195,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135113594</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17547,6 +18307,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135113607</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17654,6 +18419,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135113613</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -17761,6 +18531,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135113625</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -17868,6 +18643,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135113703</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -17975,6 +18755,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135113704</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -18082,6 +18867,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261587</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -18189,6 +18979,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261607</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -18305,6 +19100,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135282296</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -18417,6 +19217,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134934512</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18529,8 +19334,176 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261588</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 29336-2026 artfynd.xlsx
+++ b/artfynd/A 29336-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134934447</v>
       </c>
       <c r="B2" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>134934448</v>
       </c>
       <c r="B3" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>134934462</v>
       </c>
       <c r="B4" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135113596</v>
       </c>
       <c r="B5" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135115205</v>
       </c>
       <c r="B6" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>135115212</v>
       </c>
       <c r="B7" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>135261522</v>
       </c>
       <c r="B8" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>134934475</v>
       </c>
       <c r="B9" t="n">
-        <v>85592</v>
+        <v>85632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>134934472</v>
       </c>
       <c r="B10" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>134934474</v>
       </c>
       <c r="B11" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>134934486</v>
       </c>
       <c r="B12" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>134934470</v>
       </c>
       <c r="B13" t="n">
-        <v>92406</v>
+        <v>92448</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>135113602</v>
       </c>
       <c r="B14" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>135113611</v>
       </c>
       <c r="B15" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>135261584</v>
       </c>
       <c r="B16" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>134934458</v>
       </c>
       <c r="B17" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>134934460</v>
       </c>
       <c r="B18" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>134934461</v>
       </c>
       <c r="B19" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>134934463</v>
       </c>
       <c r="B20" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>134934464</v>
       </c>
       <c r="B21" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>134934466</v>
       </c>
       <c r="B22" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>134934485</v>
       </c>
       <c r="B23" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>134934495</v>
       </c>
       <c r="B24" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>134934496</v>
       </c>
       <c r="B25" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>134934497</v>
       </c>
       <c r="B26" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>134934500</v>
       </c>
       <c r="B27" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>134934504</v>
       </c>
       <c r="B28" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>134934509</v>
       </c>
       <c r="B29" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>134934511</v>
       </c>
       <c r="B30" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>454466</v>
       </c>
       <c r="R30" t="n">
-        <v>6785692</v>
+        <v>6785691</v>
       </c>
       <c r="S30" t="n">
         <v>7</v>
@@ -4032,7 +4032,7 @@
         <v>135066305</v>
       </c>
       <c r="B31" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>135066344</v>
       </c>
       <c r="B32" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4276,7 +4276,7 @@
         <v>135066346</v>
       </c>
       <c r="B33" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>135066365</v>
       </c>
       <c r="B34" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         <v>135066367</v>
       </c>
       <c r="B35" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>135113592</v>
       </c>
       <c r="B36" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>135113595</v>
       </c>
       <c r="B37" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>135113597</v>
       </c>
       <c r="B38" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         <v>135113599</v>
       </c>
       <c r="B39" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>135113604</v>
       </c>
       <c r="B40" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v>135113609</v>
       </c>
       <c r="B41" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>135113612</v>
       </c>
       <c r="B42" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>135113628</v>
       </c>
       <c r="B43" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         <v>135113630</v>
       </c>
       <c r="B44" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>135113661</v>
       </c>
       <c r="B45" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>135113702</v>
       </c>
       <c r="B46" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         <v>135115208</v>
       </c>
       <c r="B47" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>135115210</v>
       </c>
       <c r="B48" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>135115214</v>
       </c>
       <c r="B49" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>135115218</v>
       </c>
       <c r="B50" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>135115225</v>
       </c>
       <c r="B51" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         <v>135261576</v>
       </c>
       <c r="B52" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>135261578</v>
       </c>
       <c r="B53" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6713,7 +6713,7 @@
         <v>135261589</v>
       </c>
       <c r="B54" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>135261593</v>
       </c>
       <c r="B55" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>135261596</v>
       </c>
       <c r="B56" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         <v>135261597</v>
       </c>
       <c r="B57" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
         <v>135261599</v>
       </c>
       <c r="B58" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>135261600</v>
       </c>
       <c r="B59" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>135261601</v>
       </c>
       <c r="B60" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         <v>135261602</v>
       </c>
       <c r="B61" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>134934518</v>
       </c>
       <c r="B62" t="n">
-        <v>75468</v>
+        <v>75504</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>135261604</v>
       </c>
       <c r="B63" t="n">
-        <v>75468</v>
+        <v>75504</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>135113601</v>
       </c>
       <c r="B64" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
         <v>135261520</v>
       </c>
       <c r="B65" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         <v>134934455</v>
       </c>
       <c r="B66" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         <v>134934516</v>
       </c>
       <c r="B67" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>134934520</v>
       </c>
       <c r="B68" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>135066308</v>
       </c>
       <c r="B69" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>135066353</v>
       </c>
       <c r="B70" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>135113623</v>
       </c>
       <c r="B71" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>135113675</v>
       </c>
       <c r="B72" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>135115215</v>
       </c>
       <c r="B73" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>135115247</v>
       </c>
       <c r="B74" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         <v>135115277</v>
       </c>
       <c r="B75" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>135261518</v>
       </c>
       <c r="B76" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>135261519</v>
       </c>
       <c r="B77" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>135261521</v>
       </c>
       <c r="B78" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9603,7 +9603,7 @@
         <v>135261595</v>
       </c>
       <c r="B79" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>135261606</v>
       </c>
       <c r="B80" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9837,7 +9837,7 @@
         <v>135282299</v>
       </c>
       <c r="B81" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>135113657</v>
       </c>
       <c r="B82" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10071,7 +10071,7 @@
         <v>135113674</v>
       </c>
       <c r="B83" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         <v>135261577</v>
       </c>
       <c r="B84" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10429,7 +10429,7 @@
         <v>135113626</v>
       </c>
       <c r="B86" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>135113610</v>
       </c>
       <c r="B87" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>134934442</v>
       </c>
       <c r="B88" t="n">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         <v>134934450</v>
       </c>
       <c r="B89" t="n">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>135115216</v>
       </c>
       <c r="B90" t="n">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>135261608</v>
       </c>
       <c r="B91" t="n">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         <v>135282292</v>
       </c>
       <c r="B92" t="n">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         <v>135282294</v>
       </c>
       <c r="B93" t="n">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11386,7 +11386,7 @@
         <v>135282347</v>
       </c>
       <c r="B94" t="n">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11508,7 +11508,7 @@
         <v>134934491</v>
       </c>
       <c r="B95" t="n">
-        <v>56539</v>
+        <v>56544</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11625,7 +11625,7 @@
         <v>134934508</v>
       </c>
       <c r="B96" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11737,7 +11737,7 @@
         <v>135066350</v>
       </c>
       <c r="B97" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         <v>135066358</v>
       </c>
       <c r="B98" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>135113660</v>
       </c>
       <c r="B99" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>135282298</v>
       </c>
       <c r="B100" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>134934459</v>
       </c>
       <c r="B101" t="n">
-        <v>111153</v>
+        <v>111210</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>134934471</v>
       </c>
       <c r="B102" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>134934494</v>
       </c>
       <c r="B103" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>134934505</v>
       </c>
       <c r="B104" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12669,7 +12669,7 @@
         <v>134934507</v>
       </c>
       <c r="B105" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>134934510</v>
       </c>
       <c r="B106" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12911,7 +12911,7 @@
         <v>134934513</v>
       </c>
       <c r="B107" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12955,7 +12955,7 @@
         <v>454466</v>
       </c>
       <c r="R107" t="n">
-        <v>6785692</v>
+        <v>6785691</v>
       </c>
       <c r="S107" t="n">
         <v>9</v>
@@ -13032,7 +13032,7 @@
         <v>134934519</v>
       </c>
       <c r="B108" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13153,7 +13153,7 @@
         <v>134934521</v>
       </c>
       <c r="B109" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13274,7 +13274,7 @@
         <v>135066302</v>
       </c>
       <c r="B110" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13395,7 +13395,7 @@
         <v>135066303</v>
       </c>
       <c r="B111" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>135066361</v>
       </c>
       <c r="B112" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
         <v>135066364</v>
       </c>
       <c r="B113" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13758,7 +13758,7 @@
         <v>135113598</v>
       </c>
       <c r="B114" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>135113606</v>
       </c>
       <c r="B115" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>135113658</v>
       </c>
       <c r="B116" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         <v>135115221</v>
       </c>
       <c r="B117" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>135282297</v>
       </c>
       <c r="B118" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14371,7 +14371,7 @@
         <v>134934523</v>
       </c>
       <c r="B119" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14483,7 +14483,7 @@
         <v>135066357</v>
       </c>
       <c r="B120" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14595,7 +14595,7 @@
         <v>135113591</v>
       </c>
       <c r="B121" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14707,7 +14707,7 @@
         <v>135115213</v>
       </c>
       <c r="B122" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>134934449</v>
       </c>
       <c r="B123" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>135066359</v>
       </c>
       <c r="B124" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
         <v>135066363</v>
       </c>
       <c r="B125" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
         <v>135113605</v>
       </c>
       <c r="B126" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
         <v>135113701</v>
       </c>
       <c r="B127" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15379,7 +15379,7 @@
         <v>135115204</v>
       </c>
       <c r="B128" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15491,7 +15491,7 @@
         <v>135115248</v>
       </c>
       <c r="B129" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15603,7 +15603,7 @@
         <v>135261580</v>
       </c>
       <c r="B130" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15715,7 +15715,7 @@
         <v>135261592</v>
       </c>
       <c r="B131" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>135261594</v>
       </c>
       <c r="B132" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15939,7 +15939,7 @@
         <v>135282290</v>
       </c>
       <c r="B133" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>135282295</v>
       </c>
       <c r="B134" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16172,7 +16172,7 @@
         <v>134934453</v>
       </c>
       <c r="B135" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>134934465</v>
       </c>
       <c r="B136" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16396,7 +16396,7 @@
         <v>134934467</v>
       </c>
       <c r="B137" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16508,7 +16508,7 @@
         <v>134934468</v>
       </c>
       <c r="B138" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>134934469</v>
       </c>
       <c r="B139" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>134934473</v>
       </c>
       <c r="B140" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16844,7 +16844,7 @@
         <v>134934490</v>
       </c>
       <c r="B141" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16956,7 +16956,7 @@
         <v>134934498</v>
       </c>
       <c r="B142" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17068,7 +17068,7 @@
         <v>134934515</v>
       </c>
       <c r="B143" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17180,7 +17180,7 @@
         <v>134934517</v>
       </c>
       <c r="B144" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>134934522</v>
       </c>
       <c r="B145" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>134934524</v>
       </c>
       <c r="B146" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17516,7 +17516,7 @@
         <v>135066304</v>
       </c>
       <c r="B147" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17628,7 +17628,7 @@
         <v>135066306</v>
       </c>
       <c r="B148" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17740,7 +17740,7 @@
         <v>135066348</v>
       </c>
       <c r="B149" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17861,7 +17861,7 @@
         <v>135066349</v>
       </c>
       <c r="B150" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17982,7 +17982,7 @@
         <v>135066351</v>
       </c>
       <c r="B151" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
         <v>135113594</v>
       </c>
       <c r="B152" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18206,7 +18206,7 @@
         <v>135113607</v>
       </c>
       <c r="B153" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18318,7 +18318,7 @@
         <v>135113613</v>
       </c>
       <c r="B154" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18430,7 +18430,7 @@
         <v>135113625</v>
       </c>
       <c r="B155" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18542,7 +18542,7 @@
         <v>135113703</v>
       </c>
       <c r="B156" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18654,7 +18654,7 @@
         <v>135113704</v>
       </c>
       <c r="B157" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18766,7 +18766,7 @@
         <v>135261587</v>
       </c>
       <c r="B158" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18878,7 +18878,7 @@
         <v>135261607</v>
       </c>
       <c r="B159" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18990,7 +18990,7 @@
         <v>135282296</v>
       </c>
       <c r="B160" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19111,7 +19111,7 @@
         <v>134934512</v>
       </c>
       <c r="B161" t="n">
-        <v>103907</v>
+        <v>103958</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>454466</v>
       </c>
       <c r="R161" t="n">
-        <v>6785692</v>
+        <v>6785691</v>
       </c>
       <c r="S161" t="n">
         <v>7</v>
@@ -19228,7 +19228,7 @@
         <v>135261588</v>
       </c>
       <c r="B162" t="n">
-        <v>103907</v>
+        <v>103958</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>

--- a/artfynd/A 29336-2026 artfynd.xlsx
+++ b/artfynd/A 29336-2026 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>135113596</v>
       </c>
       <c r="B5" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135115205</v>
       </c>
       <c r="B6" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>135115212</v>
       </c>
       <c r="B7" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>135261522</v>
       </c>
       <c r="B8" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>135113602</v>
       </c>
       <c r="B14" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>135113611</v>
       </c>
       <c r="B15" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>135261584</v>
       </c>
       <c r="B16" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>135066305</v>
       </c>
       <c r="B31" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>135066344</v>
       </c>
       <c r="B32" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4276,7 +4276,7 @@
         <v>135066346</v>
       </c>
       <c r="B33" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>135066365</v>
       </c>
       <c r="B34" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         <v>135066367</v>
       </c>
       <c r="B35" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>135113592</v>
       </c>
       <c r="B36" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>135113595</v>
       </c>
       <c r="B37" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>135113597</v>
       </c>
       <c r="B38" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         <v>135113599</v>
       </c>
       <c r="B39" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>135113604</v>
       </c>
       <c r="B40" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v>135113609</v>
       </c>
       <c r="B41" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>135113612</v>
       </c>
       <c r="B42" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>135113628</v>
       </c>
       <c r="B43" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         <v>135113630</v>
       </c>
       <c r="B44" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>135113661</v>
       </c>
       <c r="B45" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>135113702</v>
       </c>
       <c r="B46" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         <v>135115208</v>
       </c>
       <c r="B47" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>135115210</v>
       </c>
       <c r="B48" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>135115214</v>
       </c>
       <c r="B49" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>135115218</v>
       </c>
       <c r="B50" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>135115225</v>
       </c>
       <c r="B51" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         <v>135261576</v>
       </c>
       <c r="B52" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>135261578</v>
       </c>
       <c r="B53" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6713,7 +6713,7 @@
         <v>135261589</v>
       </c>
       <c r="B54" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>135261593</v>
       </c>
       <c r="B55" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>135261596</v>
       </c>
       <c r="B56" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         <v>135261597</v>
       </c>
       <c r="B57" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
         <v>135261599</v>
       </c>
       <c r="B58" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>135261600</v>
       </c>
       <c r="B59" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>135261601</v>
       </c>
       <c r="B60" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         <v>135261602</v>
       </c>
       <c r="B61" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>135261604</v>
       </c>
       <c r="B63" t="n">
-        <v>75504</v>
+        <v>75531</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>135113601</v>
       </c>
       <c r="B64" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
         <v>135261520</v>
       </c>
       <c r="B65" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -11737,7 +11737,7 @@
         <v>135066350</v>
       </c>
       <c r="B97" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         <v>135066358</v>
       </c>
       <c r="B98" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>135113660</v>
       </c>
       <c r="B99" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>135282298</v>
       </c>
       <c r="B100" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13274,7 +13274,7 @@
         <v>135066302</v>
       </c>
       <c r="B110" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13395,7 +13395,7 @@
         <v>135066303</v>
       </c>
       <c r="B111" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>135066361</v>
       </c>
       <c r="B112" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
         <v>135066364</v>
       </c>
       <c r="B113" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13758,7 +13758,7 @@
         <v>135113598</v>
       </c>
       <c r="B114" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>135113606</v>
       </c>
       <c r="B115" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>135113658</v>
       </c>
       <c r="B116" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         <v>135115221</v>
       </c>
       <c r="B117" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>135282297</v>
       </c>
       <c r="B118" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14483,7 +14483,7 @@
         <v>135066357</v>
       </c>
       <c r="B120" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14595,7 +14595,7 @@
         <v>135113591</v>
       </c>
       <c r="B121" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14707,7 +14707,7 @@
         <v>135115213</v>
       </c>
       <c r="B122" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>135066359</v>
       </c>
       <c r="B124" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
         <v>135066363</v>
       </c>
       <c r="B125" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
         <v>135113605</v>
       </c>
       <c r="B126" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
         <v>135113701</v>
       </c>
       <c r="B127" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15379,7 +15379,7 @@
         <v>135115204</v>
       </c>
       <c r="B128" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15491,7 +15491,7 @@
         <v>135115248</v>
       </c>
       <c r="B129" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15603,7 +15603,7 @@
         <v>135261580</v>
       </c>
       <c r="B130" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15715,7 +15715,7 @@
         <v>135261592</v>
       </c>
       <c r="B131" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>135261594</v>
       </c>
       <c r="B132" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15939,7 +15939,7 @@
         <v>135282290</v>
       </c>
       <c r="B133" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>135282295</v>
       </c>
       <c r="B134" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -17516,7 +17516,7 @@
         <v>135066304</v>
       </c>
       <c r="B147" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17628,7 +17628,7 @@
         <v>135066306</v>
       </c>
       <c r="B148" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17740,7 +17740,7 @@
         <v>135066348</v>
       </c>
       <c r="B149" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17861,7 +17861,7 @@
         <v>135066349</v>
       </c>
       <c r="B150" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17982,7 +17982,7 @@
         <v>135066351</v>
       </c>
       <c r="B151" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
         <v>135113594</v>
       </c>
       <c r="B152" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18206,7 +18206,7 @@
         <v>135113607</v>
       </c>
       <c r="B153" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18318,7 +18318,7 @@
         <v>135113613</v>
       </c>
       <c r="B154" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18430,7 +18430,7 @@
         <v>135113625</v>
       </c>
       <c r="B155" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18542,7 +18542,7 @@
         <v>135113703</v>
       </c>
       <c r="B156" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18654,7 +18654,7 @@
         <v>135113704</v>
       </c>
       <c r="B157" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18766,7 +18766,7 @@
         <v>135261587</v>
       </c>
       <c r="B158" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18878,7 +18878,7 @@
         <v>135261607</v>
       </c>
       <c r="B159" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18990,7 +18990,7 @@
         <v>135282296</v>
       </c>
       <c r="B160" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19228,7 +19228,7 @@
         <v>135261588</v>
       </c>
       <c r="B162" t="n">
-        <v>103958</v>
+        <v>103985</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>

--- a/artfynd/A 29336-2026 artfynd.xlsx
+++ b/artfynd/A 29336-2026 artfynd.xlsx
@@ -2324,7 +2324,7 @@
         <v>135261584</v>
       </c>
       <c r="B16" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>135282298</v>
       </c>
       <c r="B100" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>135282297</v>
       </c>
       <c r="B118" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -15603,7 +15603,7 @@
         <v>135261580</v>
       </c>
       <c r="B130" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15715,7 +15715,7 @@
         <v>135261592</v>
       </c>
       <c r="B131" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>135261594</v>
       </c>
       <c r="B132" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15939,7 +15939,7 @@
         <v>135282290</v>
       </c>
       <c r="B133" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>135282295</v>
       </c>
       <c r="B134" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -18766,7 +18766,7 @@
         <v>135261587</v>
       </c>
       <c r="B158" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18878,7 +18878,7 @@
         <v>135261607</v>
       </c>
       <c r="B159" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18990,7 +18990,7 @@
         <v>135282296</v>
       </c>
       <c r="B160" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19228,7 +19228,7 @@
         <v>135261588</v>
       </c>
       <c r="B162" t="n">
-        <v>103990</v>
+        <v>103992</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
